--- a/课程设计.xlsx
+++ b/课程设计.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\公共交通课程设计\ggjt\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18436A11-2FE9-44F2-A37E-3E27511CC89A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13380"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +43,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>/h</t>
     </r>
@@ -66,7 +72,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>/</t>
     </r>
@@ -89,7 +95,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>/h</t>
     </r>
@@ -103,7 +109,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>/</t>
     </r>
@@ -126,7 +132,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>/min</t>
     </r>
@@ -291,15 +297,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="h:mm;@"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <numFmts count="1">
+    <numFmt numFmtId="178" formatCode="h:mm;@"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -317,13 +319,13 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="14"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="10.5"/>
@@ -340,345 +342,21 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="13">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -738,255 +416,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1017,13 +453,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -1032,93 +468,159 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
       <border>
@@ -1129,7 +631,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="0"/>
       </font>
       <fill>
@@ -1157,161 +659,47 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.39994506668294322"/>
         </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="16"/>
+      <tableStyleElement type="headerRow" dxfId="15"/>
+      <tableStyleElement type="totalRow" dxfId="14"/>
+      <tableStyleElement type="firstColumn" dxfId="13"/>
+      <tableStyleElement type="lastColumn" dxfId="12"/>
+      <tableStyleElement type="firstRowStripe" dxfId="11"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="9"/>
+      <tableStyleElement type="totalRow" dxfId="8"/>
+      <tableStyleElement type="firstRowStripe" dxfId="7"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
+      <tableStyleElement type="pageFieldValues" dxfId="0"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
@@ -1325,9 +713,15 @@
       <xdr:row>98</xdr:row>
       <xdr:rowOff>91440</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="4" name="直接连接符 3"/>
+        <xdr:cNvPr id="4" name="直接连接符 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -1369,9 +763,15 @@
       <xdr:row>99</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="5" name="直接连接符 4"/>
+        <xdr:cNvPr id="5" name="直接连接符 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -1413,9 +813,15 @@
       <xdr:row>100</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="7" name="直接连接符 6"/>
+        <xdr:cNvPr id="7" name="直接连接符 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000007000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -1457,9 +863,15 @@
       <xdr:row>101</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="8" name="直接连接符 7"/>
+        <xdr:cNvPr id="8" name="直接连接符 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000008000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -1501,9 +913,15 @@
       <xdr:row>102</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="9" name="直接连接符 8"/>
+        <xdr:cNvPr id="9" name="直接连接符 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000009000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -1545,9 +963,15 @@
       <xdr:row>103</xdr:row>
       <xdr:rowOff>121920</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="10" name="直接连接符 9"/>
+        <xdr:cNvPr id="10" name="直接连接符 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -1589,9 +1013,15 @@
       <xdr:row>104</xdr:row>
       <xdr:rowOff>121920</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="11" name="直接连接符 10"/>
+        <xdr:cNvPr id="11" name="直接连接符 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -1633,9 +1063,15 @@
       <xdr:row>105</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="12" name="直接连接符 11"/>
+        <xdr:cNvPr id="12" name="直接连接符 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -1677,9 +1113,15 @@
       <xdr:row>106</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="13" name="直接连接符 12"/>
+        <xdr:cNvPr id="13" name="直接连接符 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -1721,9 +1163,15 @@
       <xdr:row>107</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="14" name="直接连接符 13"/>
+        <xdr:cNvPr id="14" name="直接连接符 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -1765,9 +1213,15 @@
       <xdr:row>107</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="15" name="直接连接符 14"/>
+        <xdr:cNvPr id="15" name="直接连接符 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -1809,9 +1263,15 @@
       <xdr:row>108</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="16" name="直接连接符 15"/>
+        <xdr:cNvPr id="16" name="直接连接符 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000010000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -1853,9 +1313,15 @@
       <xdr:row>105</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="17" name="直接连接符 16"/>
+        <xdr:cNvPr id="17" name="直接连接符 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000011000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -2131,24 +1597,25 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q109"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="26.7777777777778" customWidth="1"/>
-    <col min="2" max="2" width="13.5555555555556" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="16.4444444444444" customWidth="1"/>
-    <col min="5" max="5" width="14.1111111111111" customWidth="1"/>
-    <col min="6" max="6" width="15.2222222222222" customWidth="1"/>
+    <col min="1" max="1" width="21.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.75" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="5" bestFit="1" customWidth="1"/>
+    <col min="10" max="16" width="5.875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.35" spans="1:6">
+    <row r="1" spans="1:6" ht="36.75" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2168,7 +1635,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" ht="14.55" spans="1:6">
+    <row r="2" spans="1:6" ht="24.75" x14ac:dyDescent="0.15">
       <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
@@ -2188,7 +1655,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="3" ht="15.15" spans="1:6">
+    <row r="3" spans="1:6" ht="24.75" x14ac:dyDescent="0.15">
       <c r="A3" s="3" t="s">
         <v>7</v>
       </c>
@@ -2208,7 +1675,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" ht="14.55" spans="1:6">
+    <row r="4" spans="1:6" ht="24.75" x14ac:dyDescent="0.15">
       <c r="A4" s="3" t="s">
         <v>8</v>
       </c>
@@ -2228,7 +1695,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" ht="14.55" spans="1:6">
+    <row r="5" spans="1:6" ht="36.75" x14ac:dyDescent="0.15">
       <c r="A5" s="5" t="s">
         <v>9</v>
       </c>
@@ -2248,7 +1715,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" ht="29.1" spans="1:6">
+    <row r="6" spans="1:6" ht="36.75" x14ac:dyDescent="0.15">
       <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
@@ -2268,7 +1735,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" ht="14.55" spans="1:6">
+    <row r="7" spans="1:6" ht="24.75" x14ac:dyDescent="0.15">
       <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
@@ -2288,7 +1755,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="8" ht="15.15" spans="1:6">
+    <row r="8" spans="1:6" ht="24.75" x14ac:dyDescent="0.15">
       <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
@@ -2308,7 +1775,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" ht="14.55" spans="1:6">
+    <row r="9" spans="1:6" ht="24.75" x14ac:dyDescent="0.15">
       <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
@@ -2328,7 +1795,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" ht="14.55" spans="1:6">
+    <row r="10" spans="1:6" ht="36.75" x14ac:dyDescent="0.15">
       <c r="A10" s="5" t="s">
         <v>9</v>
       </c>
@@ -2348,7 +1815,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" ht="29.1" spans="1:6">
+    <row r="11" spans="1:6" ht="36.75" x14ac:dyDescent="0.15">
       <c r="A11" s="3" t="s">
         <v>0</v>
       </c>
@@ -2366,7 +1833,7 @@
       </c>
       <c r="F11" s="4"/>
     </row>
-    <row r="12" ht="14.55" spans="1:6">
+    <row r="12" spans="1:6" ht="24.75" x14ac:dyDescent="0.15">
       <c r="A12" s="3" t="s">
         <v>6</v>
       </c>
@@ -2384,7 +1851,7 @@
       </c>
       <c r="F12" s="4"/>
     </row>
-    <row r="13" ht="15.15" spans="1:6">
+    <row r="13" spans="1:6" ht="24.75" x14ac:dyDescent="0.15">
       <c r="A13" s="3" t="s">
         <v>7</v>
       </c>
@@ -2402,7 +1869,7 @@
       </c>
       <c r="F13" s="4"/>
     </row>
-    <row r="14" ht="14.55" spans="1:6">
+    <row r="14" spans="1:6" ht="24.75" x14ac:dyDescent="0.15">
       <c r="A14" s="3" t="s">
         <v>8</v>
       </c>
@@ -2420,7 +1887,7 @@
       </c>
       <c r="F14" s="4"/>
     </row>
-    <row r="15" ht="14.55" spans="1:6">
+    <row r="15" spans="1:6" ht="36.75" x14ac:dyDescent="0.15">
       <c r="A15" s="3" t="s">
         <v>9</v>
       </c>
@@ -2438,17 +1905,17 @@
       </c>
       <c r="F15" s="4"/>
     </row>
-    <row r="16" ht="18" spans="1:6">
+    <row r="16" spans="1:6" ht="18.75" x14ac:dyDescent="0.15">
       <c r="A16" s="8" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="18" ht="15.15" spans="1:9">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A18" s="9" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="19" ht="29.55" spans="1:9">
+    <row r="19" spans="1:9" ht="25.5" x14ac:dyDescent="0.15">
       <c r="A19" s="10" t="s">
         <v>21</v>
       </c>
@@ -2477,7 +1944,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="20" spans="1:9">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A20" s="12" t="s">
         <v>28</v>
       </c>
@@ -2506,7 +1973,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:9">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A21" s="12" t="s">
         <v>29</v>
       </c>
@@ -2535,7 +2002,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="22" spans="1:9">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A22" s="12" t="s">
         <v>30</v>
       </c>
@@ -2564,7 +2031,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A23" s="12" t="s">
         <v>31</v>
       </c>
@@ -2593,7 +2060,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="1:9">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A24" s="12" t="s">
         <v>32</v>
       </c>
@@ -2623,7 +2090,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="25" spans="1:9">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A25" s="12" t="s">
         <v>33</v>
       </c>
@@ -2653,7 +2120,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="26" spans="1:9">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A26" s="12" t="s">
         <v>34</v>
       </c>
@@ -2683,7 +2150,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="27" spans="1:9">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A27" s="12" t="s">
         <v>35</v>
       </c>
@@ -2713,7 +2180,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:9">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A28" s="12" t="s">
         <v>36</v>
       </c>
@@ -2743,7 +2210,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="29" spans="1:9">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A29" s="12" t="s">
         <v>37</v>
       </c>
@@ -2773,7 +2240,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:9">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A30" s="12" t="s">
         <v>38</v>
       </c>
@@ -2803,7 +2270,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:9">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A31" s="12" t="s">
         <v>39</v>
       </c>
@@ -2833,7 +2300,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="32" spans="1:9">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A32" s="12" t="s">
         <v>40</v>
       </c>
@@ -2863,7 +2330,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="1:9">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A33" s="12" t="s">
         <v>41</v>
       </c>
@@ -2893,7 +2360,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="34" spans="1:9">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A34" s="12" t="s">
         <v>42</v>
       </c>
@@ -2923,7 +2390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:9">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B35" s="10"/>
       <c r="C35" s="10"/>
       <c r="D35" s="10"/>
@@ -2932,8 +2399,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="36" ht="15.15"/>
-    <row r="37" ht="29.55" spans="1:9">
+    <row r="37" spans="1:9" ht="25.5" x14ac:dyDescent="0.15">
       <c r="A37" s="9" t="s">
         <v>43</v>
       </c>
@@ -2962,12 +2428,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="38" spans="1:9">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A38" s="10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="39" spans="1:9">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A39" s="12" t="s">
         <v>28</v>
       </c>
@@ -2998,7 +2464,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="40" spans="1:9">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A40" s="12" t="s">
         <v>29</v>
       </c>
@@ -3019,7 +2485,7 @@
         <v>0</v>
       </c>
       <c r="G40">
-        <f t="shared" ref="G40:G53" si="2">(C40+E40)/2</f>
+        <f t="shared" ref="G40:G52" si="2">(C40+E40)/2</f>
         <v>1</v>
       </c>
       <c r="H40">
@@ -3030,7 +2496,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="41" spans="1:9">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A41" s="12" t="s">
         <v>30</v>
       </c>
@@ -3062,7 +2528,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="42" spans="1:9">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A42" s="12" t="s">
         <v>31</v>
       </c>
@@ -3093,7 +2559,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="43" spans="1:9">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A43" s="12" t="s">
         <v>32</v>
       </c>
@@ -3124,7 +2590,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:9">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A44" s="12" t="s">
         <v>33</v>
       </c>
@@ -3156,7 +2622,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="45" spans="1:9">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A45" s="12" t="s">
         <v>34</v>
       </c>
@@ -3187,7 +2653,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="46" spans="1:9">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A46" s="12" t="s">
         <v>35</v>
       </c>
@@ -3218,7 +2684,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="47" spans="1:9">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A47" s="12" t="s">
         <v>36</v>
       </c>
@@ -3250,7 +2716,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="48" spans="1:9">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A48" s="12" t="s">
         <v>37</v>
       </c>
@@ -3282,7 +2748,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="49" spans="1:9">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A49" s="12" t="s">
         <v>38</v>
       </c>
@@ -3314,7 +2780,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="50" spans="1:9">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A50" s="12" t="s">
         <v>39</v>
       </c>
@@ -3345,7 +2811,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="51" spans="1:9">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A51" s="12" t="s">
         <v>40</v>
       </c>
@@ -3376,7 +2842,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="52" spans="1:9">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A52" s="12" t="s">
         <v>41</v>
       </c>
@@ -3408,7 +2874,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="53" spans="1:9">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A53" s="12" t="s">
         <v>42</v>
       </c>
@@ -3439,8 +2905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" ht="15.15"/>
-    <row r="55" ht="29.55" spans="1:9">
+    <row r="55" spans="1:9" ht="25.5" x14ac:dyDescent="0.15">
       <c r="A55" s="13" t="s">
         <v>44</v>
       </c>
@@ -3469,12 +2934,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="56" spans="1:9">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A56" s="10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="57" spans="1:9">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A57" s="12" t="s">
         <v>28</v>
       </c>
@@ -3505,7 +2970,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="58" spans="1:9">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A58" s="12" t="s">
         <v>29</v>
       </c>
@@ -3536,7 +3001,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="59" spans="1:9">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A59" s="12" t="s">
         <v>30</v>
       </c>
@@ -3567,7 +3032,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="60" spans="1:9">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A60" s="12" t="s">
         <v>31</v>
       </c>
@@ -3598,7 +3063,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="61" spans="1:9">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A61" s="12" t="s">
         <v>32</v>
       </c>
@@ -3615,7 +3080,7 @@
         <v>2</v>
       </c>
       <c r="F61">
-        <f t="shared" ref="F58:F71" si="6">(B61+D61)/2</f>
+        <f t="shared" ref="F61:F71" si="6">(B61+D61)/2</f>
         <v>3</v>
       </c>
       <c r="G61">
@@ -3630,7 +3095,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="62" spans="1:9">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A62" s="12" t="s">
         <v>33</v>
       </c>
@@ -3661,7 +3126,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="63" spans="1:9">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A63" s="12" t="s">
         <v>34</v>
       </c>
@@ -3693,7 +3158,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="64" spans="1:9">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A64" s="12" t="s">
         <v>35</v>
       </c>
@@ -3724,7 +3189,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="65" spans="1:9">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A65" s="12" t="s">
         <v>36</v>
       </c>
@@ -3754,7 +3219,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="66" spans="1:9">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A66" s="12" t="s">
         <v>37</v>
       </c>
@@ -3786,7 +3251,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="67" spans="1:9">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A67" s="12" t="s">
         <v>38</v>
       </c>
@@ -3818,7 +3283,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="68" spans="1:9">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A68" s="12" t="s">
         <v>39</v>
       </c>
@@ -3849,7 +3314,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="69" spans="1:9">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A69" s="12" t="s">
         <v>40</v>
       </c>
@@ -3880,7 +3345,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="70" spans="1:9">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A70" s="12" t="s">
         <v>41</v>
       </c>
@@ -3910,7 +3375,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="71" spans="1:9">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A71" s="12" t="s">
         <v>42</v>
       </c>
@@ -3942,7 +3407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" ht="29.55" spans="1:9">
+    <row r="73" spans="1:9" ht="25.5" x14ac:dyDescent="0.15">
       <c r="A73" t="s">
         <v>45</v>
       </c>
@@ -3971,12 +3436,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="74" spans="1:9">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A74" s="10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="75" spans="1:9">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A75" s="12" t="s">
         <v>28</v>
       </c>
@@ -4007,7 +3472,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="76" spans="1:9">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A76" s="12" t="s">
         <v>29</v>
       </c>
@@ -4028,7 +3493,7 @@
         <v>0</v>
       </c>
       <c r="G76">
-        <f t="shared" ref="G76:G89" si="8">(C76+E76)/2</f>
+        <f t="shared" ref="G76:G88" si="8">(C76+E76)/2</f>
         <v>1</v>
       </c>
       <c r="H76">
@@ -4039,7 +3504,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="77" spans="1:9">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A77" s="12" t="s">
         <v>30</v>
       </c>
@@ -4071,7 +3536,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="78" spans="1:9">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A78" s="12" t="s">
         <v>31</v>
       </c>
@@ -4102,7 +3567,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="79" spans="1:9">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A79" s="12" t="s">
         <v>32</v>
       </c>
@@ -4133,7 +3598,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="80" spans="1:9">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A80" s="12" t="s">
         <v>33</v>
       </c>
@@ -4164,7 +3629,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="81" spans="1:9">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A81" s="12" t="s">
         <v>34</v>
       </c>
@@ -4195,7 +3660,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="82" spans="1:9">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A82" s="12" t="s">
         <v>35</v>
       </c>
@@ -4226,7 +3691,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="83" spans="1:9">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A83" s="12" t="s">
         <v>36</v>
       </c>
@@ -4258,7 +3723,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="84" spans="1:9">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A84" s="12" t="s">
         <v>37</v>
       </c>
@@ -4290,7 +3755,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="85" spans="1:9">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A85" s="12" t="s">
         <v>38</v>
       </c>
@@ -4322,7 +3787,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="86" spans="1:9">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A86" s="12" t="s">
         <v>39</v>
       </c>
@@ -4353,7 +3818,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="87" spans="1:9">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A87" s="12" t="s">
         <v>40</v>
       </c>
@@ -4384,7 +3849,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="88" spans="1:9">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A88" s="12" t="s">
         <v>41</v>
       </c>
@@ -4416,7 +3881,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="89" spans="1:9">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A89" s="12" t="s">
         <v>42</v>
       </c>
@@ -4447,12 +3912,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" ht="15.15" spans="1:9">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A96" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="97" ht="28.35" spans="1:17">
+    <row r="97" spans="1:17" ht="25.5" x14ac:dyDescent="0.15">
       <c r="B97" t="s">
         <v>47</v>
       </c>
@@ -4502,7 +3967,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="98" ht="15.15" spans="1:17">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A98" s="14"/>
       <c r="B98" t="s">
         <v>49</v>
@@ -4550,8 +4015,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="99" spans="1:17">
-      <c r="A99" s="15" t="s">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A99" t="s">
         <v>50</v>
       </c>
       <c r="B99">
@@ -4561,7 +4026,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="100" spans="1:17">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B100">
         <v>2</v>
       </c>
@@ -4569,7 +4034,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="101" spans="1:17">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B101">
         <v>3</v>
       </c>
@@ -4577,7 +4042,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="102" spans="1:17">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B102">
         <v>4</v>
       </c>
@@ -4585,7 +4050,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="103" spans="1:17">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B103">
         <v>5</v>
       </c>
@@ -4593,7 +4058,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="104" spans="1:17">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B104">
         <v>6</v>
       </c>
@@ -4601,7 +4066,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="105" spans="1:17">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B105">
         <v>7</v>
       </c>
@@ -4609,7 +4074,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="106" spans="1:17">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B106">
         <v>8</v>
       </c>
@@ -4617,7 +4082,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:17">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B107">
         <v>9</v>
       </c>
@@ -4625,7 +4090,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="108" spans="1:17">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B108">
         <v>10</v>
       </c>
@@ -4633,7 +4098,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="109" spans="1:17">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B109">
         <v>11</v>
       </c>
@@ -4642,8 +4107,8 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>